--- a/server/tests/fixtures/broken_missing_choices.xlsx
+++ b/server/tests/fixtures/broken_missing_choices.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,11 @@
       <c r="N1" t="inlineStr">
         <is>
           <t>appearance</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>repeat_count</t>
         </is>
       </c>
     </row>
